--- a/media/file/B0F6MTPQVG/B0F6MTPQVG_ROI-US-pack.xlsx
+++ b/media/file/B0F6MTPQVG/B0F6MTPQVG_ROI-US-pack.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>238.27</t>
+          <t>113.30</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>836.05</t>
+          <t>168.60</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>418.02</t>
+          <t>84.30</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>418.02</t>
+          <t>84.30</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>125.78</t>
+          <t>546.01</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>865.38</t>
+          <t>3691.06</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>3773.46</t>
+          <t>16380.44</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>25961.40</t>
+          <t>110731.79</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>16.06</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>29.30</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -952,9 +952,21 @@
           <t>$</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>图片链接</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51tovwM4kvL._AC_US200_.jpg</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
@@ -967,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -975,9 +987,21 @@
           <t>$</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>asin链接</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/DP/B0F6MTPQVG</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
@@ -990,7 +1014,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>321.09</t>
+          <t>602.85</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -998,9 +1022,21 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1688链接</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>https://aibuy.1688.com/landingpage/home/inventory/products.html?bizType=selectionTool&amp;customerId=sellerspriteLP&amp;lang=zh&amp;currency=CNY</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
@@ -1019,7 +1055,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>110.94</t>
+          <t>499.26</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1042,7 +1078,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1065,7 +1101,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1088,7 +1124,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>56.32</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1111,7 +1147,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">

--- a/media/file/B0F6MTPQVG/B0F6MTPQVG_ROI-US-pack.xlsx
+++ b/media/file/B0F6MTPQVG/B0F6MTPQVG_ROI-US-pack.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>546.01</t>
+          <t>638.01</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>3691.06</t>
+          <t>4332.10</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>16380.44</t>
+          <t>19140.35</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>110731.79</t>
+          <t>129962.99</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>602.85</t>
+          <t>883.71</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>499.26</t>
+          <t>750.45</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>105.53</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>56.32</t>
+          <t>59.87</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">

--- a/media/file/B0F6MTPQVG/B0F6MTPQVG_ROI-US-pack.xlsx
+++ b/media/file/B0F6MTPQVG/B0F6MTPQVG_ROI-US-pack.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>638.01</t>
+          <t>377.59</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>4332.10</t>
+          <t>2563.83</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>19140.35</t>
+          <t>11327.66</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>129962.99</t>
+          <t>76914.80</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>883.71</t>
+          <t>153.20</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>750.45</t>
+          <t>117.84</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>105.53</t>
+          <t>62.46</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>59.87</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
